--- a/teste_script/documentacao/RAG CALIGARES.xlsx
+++ b/teste_script/documentacao/RAG CALIGARES.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
   <si>
     <t>Nome planilha</t>
   </si>
@@ -38,6 +38,12 @@
     <t>Planilha contendo registros de agendamentos e atendimentos da clínica odontológica 3 ao longo de alguns meses. Cada linha representa um agendamento ou interação única com um paciente. São 3 clínicas e as 3 apresentam a mesma estrutura de colunas.</t>
   </si>
   <si>
+    <t>Nome_dentistas</t>
+  </si>
+  <si>
+    <t>Planilha contendo nome dos dentistas com base em seus IDs localizados nos relatórios das clínicas.</t>
+  </si>
+  <si>
     <t>Nome da Planilha</t>
   </si>
   <si>
@@ -65,13 +71,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>A data para a qual o paciente foi agendado.</t>
+    <t>A data para a qual o paciente foi agendado. Formato ano-mês-dia.</t>
   </si>
   <si>
     <t>data de criação do agendamento</t>
   </si>
   <si>
-    <t>A data em que o registro foi inserido no sistema.</t>
+    <t>A data em que o registro foi inserido no sistema. Formato ano-mês-dia.</t>
   </si>
   <si>
     <t>nome</t>
@@ -107,13 +113,7 @@
     <t>procedimentos</t>
   </si>
   <si>
-    <t>Detalhes técnicos do procedimento.</t>
-  </si>
-  <si>
-    <t>descrição</t>
-  </si>
-  <si>
-    <t>Define o tipo de serviço agendado.</t>
+    <t>Descrição do procedimento agendado.</t>
   </si>
   <si>
     <t>status</t>
@@ -144,13 +144,22 @@
   </si>
   <si>
     <t>Nome do operador/sistema que registrou a linha.</t>
+  </si>
+  <si>
+    <t>id_dentista</t>
+  </si>
+  <si>
+    <t>nome_dentista</t>
+  </si>
+  <si>
+    <t>Nome do profissional responsável.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -171,6 +180,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -186,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -203,6 +218,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -458,6 +476,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -477,16 +503,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -494,13 +520,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +534,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -522,13 +548,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -536,13 +562,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +576,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -564,13 +590,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -578,13 +604,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -592,13 +618,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -606,13 +632,13 @@
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -620,13 +646,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -634,13 +660,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -648,13 +674,13 @@
         <v>2</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -662,13 +688,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -676,27 +702,27 @@
         <v>2</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -704,13 +730,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -718,13 +744,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -732,13 +758,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -746,13 +772,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -760,13 +786,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -774,13 +800,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -788,13 +814,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -802,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -816,13 +842,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -830,13 +856,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -844,13 +870,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -858,13 +884,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
@@ -872,41 +898,41 @@
         <v>4</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -914,13 +940,13 @@
         <v>6</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
@@ -928,13 +954,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -942,13 +968,13 @@
         <v>6</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -956,13 +982,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -970,13 +996,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
@@ -984,13 +1010,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -998,13 +1024,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1012,13 +1038,13 @@
         <v>6</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
@@ -1026,13 +1052,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -1040,13 +1066,13 @@
         <v>6</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -1054,13 +1080,13 @@
         <v>6</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -1068,24 +1094,24 @@
         <v>6</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>39</v>
@@ -1093,30 +1119,16 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
